--- a/docs/Fill_Up_Template/설비비가동사유코드_업로드양식.xlsx
+++ b/docs/Fill_Up_Template/설비비가동사유코드_업로드양식.xlsx
@@ -456,7 +456,7 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>통제가능</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>비계획</t>
+          <t>통제불가능</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>비계획</t>
+          <t>통제불가능</t>
         </is>
       </c>
     </row>
@@ -540,14 +540,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>통제가능</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 선택하세요" prompt="계획 / 비계획" type="list">
-      <formula1>"계획,비계획"</formula1>
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 선택하세요" prompt="통제가능 / 통제불가능" type="list">
+      <formula1>"통제가능,통제불가능"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>계획 / 비계획</t>
+          <t>통제가능 / 통제불가능</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>계획정지·비계획정지 구분 (드롭다운 선택)</t>
+          <t>통제가능·통제불가능 구분 (드롭다운 선택)</t>
         </is>
       </c>
     </row>

--- a/docs/Fill_Up_Template/설비비가동사유코드_업로드양식.xlsx
+++ b/docs/Fill_Up_Template/설비비가동사유코드_업로드양식.xlsx
@@ -1,54 +1,176 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/log/Desktop/04.Codai/C.Project/04.MES/01.ES_MES/docs/Fill_Up_Template/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D75D1A-2EA0-964B-9EBD-5AC63BD22917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="설비비가동사유코드" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="입력안내" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="설비비가동사유코드" sheetId="1" r:id="rId1"/>
+    <sheet name="입력안내" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+  <si>
+    <t>사유코드</t>
+  </si>
+  <si>
+    <t>사유명</t>
+  </si>
+  <si>
+    <t>사유구분</t>
+  </si>
+  <si>
+    <t>모델 교체</t>
+  </si>
+  <si>
+    <t>통제가능</t>
+  </si>
+  <si>
+    <t>자재 대기</t>
+  </si>
+  <si>
+    <t>통제불가능</t>
+  </si>
+  <si>
+    <t>설비 고장</t>
+  </si>
+  <si>
+    <t>청소/5S</t>
+  </si>
+  <si>
+    <t>항목</t>
+  </si>
+  <si>
+    <t>필수여부</t>
+  </si>
+  <si>
+    <t>허용값 / 형식</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>필수</t>
+  </si>
+  <si>
+    <t>영문·숫자</t>
+  </si>
+  <si>
+    <t>텍스트</t>
+  </si>
+  <si>
+    <t>사유 명칭</t>
+  </si>
+  <si>
+    <t>통제가능 / 통제불가능</t>
+  </si>
+  <si>
+    <t>통제가능·통제불가능 구분 (드롭다운 선택)</t>
+  </si>
+  <si>
+    <t>예) AA01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>예) MD02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>예) EE03</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>예) ZZ01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">사유 고유 코드 (중복 불가) - 영문2자리+숫자2자리 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>*은성 사내 별도 룰이 있을 경우 적용해도 무방</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,103 +184,45 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -446,107 +510,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>사유코드</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>사유명</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>사유구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DWN-CHG</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>모델 교체</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>통제가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DWN-MAT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>자재 대기</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>통제불가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DWN-BRK</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>설비 고장</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>통제불가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DWN-CLN</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>청소/5S</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>통제가능</t>
-        </is>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 선택하세요" prompt="통제가능 / 통제불가능" type="list">
+    <dataValidation type="list" allowBlank="1" error="목록에서 선택하세요" prompt="통제가능 / 통제불가능" sqref="C2:C1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"통제가능,통제불가능"</formula1>
     </dataValidation>
   </dataValidations>
@@ -555,109 +586,74 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="103.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>필수여부</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>허용값 / 형식</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>사유코드</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>영문·숫자</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>사유 고유 코드 (중복 불가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>사유명</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>텍스트</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>사유 명칭</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>사유구분</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>필수</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>통제가능 / 통제불가능</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>통제가능·통제불가능 구분 (드롭다운 선택)</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>